--- a/public/uploads/pusaka/presensi/smp.xlsx
+++ b/public/uploads/pusaka/presensi/smp.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="187">
   <si>
     <t>NAMA</t>
   </si>
@@ -80,445 +80,502 @@
     <t>Guru Ahli Muda</t>
   </si>
   <si>
-    <t>2026-08-01 00:00:00</t>
+    <t>2026-09-01 00:00:00</t>
+  </si>
+  <si>
+    <t>Selasa</t>
+  </si>
+  <si>
+    <t>7:30</t>
+  </si>
+  <si>
+    <t>6:34</t>
+  </si>
+  <si>
+    <t>16:0</t>
+  </si>
+  <si>
+    <t>18:18</t>
+  </si>
+  <si>
+    <t>SLTP Negeri dilingkungan Kabupaten Tanah Datar</t>
+  </si>
+  <si>
+    <t>Kantor Kementerian Agama Kabupaten Tanah Datar</t>
+  </si>
+  <si>
+    <t>PNS</t>
+  </si>
+  <si>
+    <t>2026-09-02 00:00:00</t>
+  </si>
+  <si>
+    <t>Rabu</t>
+  </si>
+  <si>
+    <t>6:32</t>
+  </si>
+  <si>
+    <t>16:24</t>
+  </si>
+  <si>
+    <t>2026-09-03 00:00:00</t>
+  </si>
+  <si>
+    <t>Kamis</t>
+  </si>
+  <si>
+    <t>6:33</t>
+  </si>
+  <si>
+    <t>16:27</t>
+  </si>
+  <si>
+    <t>2026-09-04 00:00:00</t>
+  </si>
+  <si>
+    <t>Jumat</t>
+  </si>
+  <si>
+    <t>6:45</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>17:7</t>
+  </si>
+  <si>
+    <t>2026-09-05 00:00:00</t>
   </si>
   <si>
     <t>Sabtu</t>
   </si>
   <si>
-    <t>SLTP Negeri dilingkungan Kabupaten Tanah Datar</t>
-  </si>
-  <si>
-    <t>Kantor Kementerian Agama Kabupaten Tanah Datar</t>
-  </si>
-  <si>
-    <t>PNS</t>
-  </si>
-  <si>
-    <t>2026-08-02 00:00:00</t>
+    <t>2026-09-06 00:00:00</t>
   </si>
   <si>
     <t>Minggu</t>
   </si>
   <si>
-    <t>2026-08-03 00:00:00</t>
+    <t>2026-09-07 00:00:00</t>
   </si>
   <si>
     <t>Senin</t>
   </si>
   <si>
-    <t>7:30</t>
+    <t>6:44</t>
+  </si>
+  <si>
+    <t>2026-09-08 00:00:00</t>
+  </si>
+  <si>
+    <t>6:29</t>
+  </si>
+  <si>
+    <t>16:40</t>
+  </si>
+  <si>
+    <t>2026-09-09 00:00:00</t>
+  </si>
+  <si>
+    <t>6:46</t>
+  </si>
+  <si>
+    <t>16:3</t>
+  </si>
+  <si>
+    <t>2026-09-10 00:00:00</t>
   </si>
   <si>
     <t>6:38</t>
   </si>
   <si>
-    <t>16:0</t>
-  </si>
-  <si>
-    <t>17:4</t>
-  </si>
-  <si>
-    <t>2026-08-04 00:00:00</t>
-  </si>
-  <si>
-    <t>Selasa</t>
+    <t>2026-09-11 00:00:00</t>
+  </si>
+  <si>
+    <t>17:28</t>
+  </si>
+  <si>
+    <t>2026-09-12 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-09-13 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 00:00:00</t>
+  </si>
+  <si>
+    <t>16:9</t>
+  </si>
+  <si>
+    <t>2026-09-15 00:00:00</t>
+  </si>
+  <si>
+    <t>6:59</t>
+  </si>
+  <si>
+    <t>16:19</t>
+  </si>
+  <si>
+    <t>2026-09-16 00:00:00</t>
+  </si>
+  <si>
+    <t>18:48</t>
+  </si>
+  <si>
+    <t>2026-09-17 00:00:00</t>
+  </si>
+  <si>
+    <t>6:20</t>
+  </si>
+  <si>
+    <t>2026-09-18 00:00:00</t>
+  </si>
+  <si>
+    <t>6:36</t>
+  </si>
+  <si>
+    <t>16:16</t>
+  </si>
+  <si>
+    <t>2026-09-19 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-09-20 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 00:00:00</t>
+  </si>
+  <si>
+    <t>6:23</t>
+  </si>
+  <si>
+    <t>16:29</t>
+  </si>
+  <si>
+    <t>2026-09-22 00:00:00</t>
+  </si>
+  <si>
+    <t>6:47</t>
+  </si>
+  <si>
+    <t>16:46</t>
+  </si>
+  <si>
+    <t>2026-09-23 00:00:00</t>
+  </si>
+  <si>
+    <t>6:24</t>
+  </si>
+  <si>
+    <t>18:2</t>
+  </si>
+  <si>
+    <t>2026-09-24 00:00:00</t>
+  </si>
+  <si>
+    <t>16:31</t>
+  </si>
+  <si>
+    <t>2026-09-25 00:00:00</t>
+  </si>
+  <si>
+    <t>6:37</t>
+  </si>
+  <si>
+    <t>19:27</t>
+  </si>
+  <si>
+    <t>2026-09-26 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-09-27 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 00:00:00</t>
+  </si>
+  <si>
+    <t>16:42</t>
+  </si>
+  <si>
+    <t>2026-09-29 00:00:00</t>
+  </si>
+  <si>
+    <t>6:19</t>
+  </si>
+  <si>
+    <t>16:5</t>
+  </si>
+  <si>
+    <t>2026-09-30 00:00:00</t>
+  </si>
+  <si>
+    <t>16:1</t>
+  </si>
+  <si>
+    <t>JASMAN EFENDI, S.Ag</t>
+  </si>
+  <si>
+    <t>197405012003121003</t>
+  </si>
+  <si>
+    <t>15:56</t>
+  </si>
+  <si>
+    <t>7:27</t>
+  </si>
+  <si>
+    <t>20:24</t>
+  </si>
+  <si>
+    <t>7:25</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>7:21</t>
+  </si>
+  <si>
+    <t>19:38</t>
+  </si>
+  <si>
+    <t>7:13</t>
+  </si>
+  <si>
+    <t>19:11</t>
+  </si>
+  <si>
+    <t>7:15</t>
+  </si>
+  <si>
+    <t>18:23</t>
+  </si>
+  <si>
+    <t>7:36</t>
+  </si>
+  <si>
+    <t>15:41</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>6:53</t>
+  </si>
+  <si>
+    <t>17:22</t>
+  </si>
+  <si>
+    <t>7:38</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>7:22</t>
+  </si>
+  <si>
+    <t>19:29</t>
+  </si>
+  <si>
+    <t>7:54</t>
+  </si>
+  <si>
+    <t>18:24</t>
+  </si>
+  <si>
+    <t>7:14</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>7:4</t>
+  </si>
+  <si>
+    <t>17:12</t>
+  </si>
+  <si>
+    <t>7:16</t>
+  </si>
+  <si>
+    <t>6:15</t>
+  </si>
+  <si>
+    <t>18:17</t>
+  </si>
+  <si>
+    <t>7:8</t>
+  </si>
+  <si>
+    <t>19:14</t>
+  </si>
+  <si>
+    <t>7:26</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>6:41</t>
+  </si>
+  <si>
+    <t>7:29</t>
+  </si>
+  <si>
+    <t>19:12</t>
+  </si>
+  <si>
+    <t>19:16</t>
+  </si>
+  <si>
+    <t>18:0</t>
+  </si>
+  <si>
+    <t>RAHMATUL KASRI, S.Pd.I</t>
+  </si>
+  <si>
+    <t>198009132005012011</t>
+  </si>
+  <si>
+    <t>7:5</t>
+  </si>
+  <si>
+    <t>16:8</t>
+  </si>
+  <si>
+    <t>7:9</t>
+  </si>
+  <si>
+    <t>16:14</t>
+  </si>
+  <si>
+    <t>7:10</t>
+  </si>
+  <si>
+    <t>17:13</t>
+  </si>
+  <si>
+    <t>7:12</t>
+  </si>
+  <si>
+    <t>16:13</t>
+  </si>
+  <si>
+    <t>17:23</t>
+  </si>
+  <si>
+    <t>7:11</t>
+  </si>
+  <si>
+    <t>16:44</t>
+  </si>
+  <si>
+    <t>16:39</t>
+  </si>
+  <si>
+    <t>7:7</t>
+  </si>
+  <si>
+    <t>16:17</t>
+  </si>
+  <si>
+    <t>16:53</t>
+  </si>
+  <si>
+    <t>16:36</t>
+  </si>
+  <si>
+    <t>21:57</t>
+  </si>
+  <si>
+    <t>17:2</t>
+  </si>
+  <si>
+    <t>16:21</t>
+  </si>
+  <si>
+    <t>16:56</t>
+  </si>
+  <si>
+    <t>16:11</t>
+  </si>
+  <si>
+    <t>17:19</t>
+  </si>
+  <si>
+    <t>16:12</t>
+  </si>
+  <si>
+    <t>RITA AFRIANTI, S.Pd.I</t>
+  </si>
+  <si>
+    <t>198106182005012003</t>
+  </si>
+  <si>
+    <t>17:17</t>
+  </si>
+  <si>
+    <t>16:43</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>7:17</t>
+  </si>
+  <si>
+    <t>17:58</t>
+  </si>
+  <si>
+    <t>6:58</t>
   </si>
   <si>
     <t>18:35</t>
   </si>
   <si>
-    <t>2026-08-05 00:00:00</t>
-  </si>
-  <si>
-    <t>Rabu</t>
-  </si>
-  <si>
-    <t>6:35</t>
-  </si>
-  <si>
-    <t>2026-08-06 00:00:00</t>
-  </si>
-  <si>
-    <t>Kamis</t>
-  </si>
-  <si>
-    <t>6:28</t>
-  </si>
-  <si>
-    <t>16:19</t>
-  </si>
-  <si>
-    <t>2026-08-07 00:00:00</t>
-  </si>
-  <si>
-    <t>Jumat</t>
-  </si>
-  <si>
-    <t>6:54</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>16:4</t>
-  </si>
-  <si>
-    <t>2026-08-08 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-08-09 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 00:00:00</t>
-  </si>
-  <si>
-    <t>6:58</t>
-  </si>
-  <si>
-    <t>16:36</t>
-  </si>
-  <si>
-    <t>2026-08-11 00:00:00</t>
-  </si>
-  <si>
-    <t>7:8</t>
-  </si>
-  <si>
-    <t>16:53</t>
-  </si>
-  <si>
-    <t>2026-08-12 00:00:00</t>
-  </si>
-  <si>
-    <t>6:51</t>
-  </si>
-  <si>
-    <t>18:29</t>
-  </si>
-  <si>
-    <t>2026-08-13 00:00:00</t>
-  </si>
-  <si>
-    <t>7:2</t>
-  </si>
-  <si>
-    <t>16:17</t>
-  </si>
-  <si>
-    <t>2026-08-14 00:00:00</t>
-  </si>
-  <si>
-    <t>7:3</t>
-  </si>
-  <si>
-    <t>16:32</t>
-  </si>
-  <si>
-    <t>2026-08-15 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-08-16 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 00:00:00</t>
-  </si>
-  <si>
-    <t>Proklamasi Kemerdekaan RI Ke 81</t>
-  </si>
-  <si>
-    <t>2026-08-18 00:00:00</t>
-  </si>
-  <si>
-    <t>6:37</t>
-  </si>
-  <si>
-    <t>2026-08-19 00:00:00</t>
-  </si>
-  <si>
-    <t>6:43</t>
-  </si>
-  <si>
-    <t>18:28</t>
-  </si>
-  <si>
-    <t>2026-08-20 00:00:00</t>
-  </si>
-  <si>
-    <t>17:39</t>
-  </si>
-  <si>
-    <t>2026-08-21 00:00:00</t>
-  </si>
-  <si>
-    <t>6:45</t>
-  </si>
-  <si>
-    <t>2026-08-22 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-08-23 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 00:00:00</t>
-  </si>
-  <si>
-    <t>6:32</t>
-  </si>
-  <si>
-    <t>16:31</t>
-  </si>
-  <si>
-    <t>2026-08-25 00:00:00</t>
-  </si>
-  <si>
-    <t>Maulid Nabi Muhammad SAW</t>
-  </si>
-  <si>
-    <t>2026-08-26 00:00:00</t>
-  </si>
-  <si>
-    <t>16:3</t>
-  </si>
-  <si>
-    <t>2026-08-27 00:00:00</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>2026-08-28 00:00:00</t>
-  </si>
-  <si>
-    <t>6:59</t>
-  </si>
-  <si>
-    <t>16:11</t>
-  </si>
-  <si>
-    <t>2026-08-29 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-08-30 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 00:00:00</t>
-  </si>
-  <si>
-    <t>6:40</t>
-  </si>
-  <si>
-    <t>16:52</t>
-  </si>
-  <si>
-    <t>JASMAN EFENDI, S.Ag</t>
-  </si>
-  <si>
-    <t>197405012003121003</t>
-  </si>
-  <si>
-    <t>7:11</t>
-  </si>
-  <si>
-    <t>15:32</t>
-  </si>
-  <si>
-    <t>7:21</t>
-  </si>
-  <si>
-    <t>7:36</t>
-  </si>
-  <si>
-    <t>21:43</t>
-  </si>
-  <si>
-    <t>7:32</t>
-  </si>
-  <si>
-    <t>17:43</t>
-  </si>
-  <si>
-    <t>19:3</t>
-  </si>
-  <si>
-    <t>7:7</t>
-  </si>
-  <si>
-    <t>18:49</t>
-  </si>
-  <si>
-    <t>7:35</t>
-  </si>
-  <si>
-    <t>20:39</t>
-  </si>
-  <si>
-    <t>7:54</t>
-  </si>
-  <si>
-    <t>7:39</t>
-  </si>
-  <si>
-    <t>18:4</t>
-  </si>
-  <si>
-    <t>7:14</t>
-  </si>
-  <si>
-    <t>19:44</t>
-  </si>
-  <si>
-    <t>7:25</t>
-  </si>
-  <si>
-    <t>16:54</t>
-  </si>
-  <si>
-    <t>7:46</t>
-  </si>
-  <si>
-    <t>19:53</t>
-  </si>
-  <si>
-    <t>7:12</t>
-  </si>
-  <si>
-    <t>17:32</t>
-  </si>
-  <si>
-    <t>7:42</t>
-  </si>
-  <si>
-    <t>21:36</t>
-  </si>
-  <si>
-    <t>19:59</t>
-  </si>
-  <si>
-    <t>7:33</t>
-  </si>
-  <si>
-    <t>Tanpa Keterangan</t>
-  </si>
-  <si>
-    <t>RAHMATUL KASRI, S.Pd.I</t>
-  </si>
-  <si>
-    <t>198009132005012011</t>
-  </si>
-  <si>
     <t>7:6</t>
   </si>
   <si>
-    <t>16:58</t>
-  </si>
-  <si>
-    <t>7:4</t>
-  </si>
-  <si>
-    <t>7:9</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>7:13</t>
-  </si>
-  <si>
-    <t>17:34</t>
-  </si>
-  <si>
-    <t>7:19</t>
-  </si>
-  <si>
-    <t>16:37</t>
-  </si>
-  <si>
-    <t>17:5</t>
-  </si>
-  <si>
-    <t>17:23</t>
-  </si>
-  <si>
-    <t>7:5</t>
-  </si>
-  <si>
-    <t>17:54</t>
-  </si>
-  <si>
-    <t>6:57</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>17:13</t>
-  </si>
-  <si>
-    <t>16:13</t>
+    <t>17:6</t>
+  </si>
+  <si>
+    <t>16:2</t>
   </si>
   <si>
     <t>17:49</t>
   </si>
   <si>
-    <t>21:6</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>RITA AFRIANTI, S.Pd.I</t>
-  </si>
-  <si>
-    <t>198106182005012003</t>
-  </si>
-  <si>
-    <t>7:28</t>
-  </si>
-  <si>
-    <t>17:6</t>
-  </si>
-  <si>
-    <t>7:10</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>16:1</t>
+    <t>17:53</t>
+  </si>
+  <si>
+    <t>17:18</t>
+  </si>
+  <si>
+    <t>19:9</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>17:9</t>
+  </si>
+  <si>
+    <t>16:57</t>
   </si>
   <si>
     <t>17:27</t>
   </si>
   <si>
-    <t>16:9</t>
-  </si>
-  <si>
-    <t>16:51</t>
-  </si>
-  <si>
-    <t>16:8</t>
-  </si>
-  <si>
-    <t>17:16</t>
-  </si>
-  <si>
-    <t>16:46</t>
-  </si>
-  <si>
-    <t>17:25</t>
-  </si>
-  <si>
-    <t>17:3</t>
-  </si>
-  <si>
-    <t>18:0</t>
-  </si>
-  <si>
-    <t>16:49</t>
-  </si>
-  <si>
-    <t>16:28</t>
+    <t>17:1</t>
+  </si>
+  <si>
+    <t>17:31</t>
   </si>
 </sst>
 </file>
@@ -858,7 +915,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:R125"/>
+  <dimension ref="A1:R121"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -933,14 +990,32 @@
       <c r="E2" t="s">
         <v>22</v>
       </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2">
+        <v>56</v>
+      </c>
+      <c r="I2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2">
+        <v>138</v>
+      </c>
       <c r="P2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -954,19 +1029,37 @@
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>31</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3">
+        <v>58</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3">
+        <v>24</v>
       </c>
       <c r="P3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -980,37 +1073,37 @@
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H4">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I4" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K4">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="P4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1024,34 +1117,37 @@
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>23</v>
+      </c>
+      <c r="G5" t="s">
+        <v>40</v>
       </c>
       <c r="H5">
-        <v>-225</v>
+        <v>45</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="J5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="K5">
-        <v>155</v>
+        <v>37</v>
       </c>
       <c r="P5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1065,34 +1161,19 @@
         <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6">
-        <v>55</v>
-      </c>
-      <c r="I6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6">
-        <v>-255</v>
+        <v>44</v>
       </c>
       <c r="P6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1106,37 +1187,19 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7">
-        <v>62</v>
-      </c>
-      <c r="I7" t="s">
-        <v>32</v>
-      </c>
-      <c r="J7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K7">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="P7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q7" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1150,37 +1213,34 @@
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8">
         <v>46</v>
       </c>
-      <c r="H8">
-        <v>36</v>
-      </c>
       <c r="I8" t="s">
-        <v>47</v>
-      </c>
-      <c r="J8" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="K8">
-        <v>-26</v>
+        <v>-255</v>
       </c>
       <c r="P8" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R8" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1194,19 +1254,37 @@
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
         <v>22</v>
       </c>
+      <c r="F9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9">
+        <v>61</v>
+      </c>
+      <c r="I9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" t="s">
+        <v>52</v>
+      </c>
+      <c r="K9">
+        <v>40</v>
+      </c>
       <c r="P9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R9" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1220,19 +1298,37 @@
         <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>31</v>
+      </c>
+      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10">
+        <v>44</v>
+      </c>
+      <c r="I10" t="s">
+        <v>25</v>
+      </c>
+      <c r="J10" t="s">
+        <v>55</v>
+      </c>
+      <c r="K10">
+        <v>3</v>
       </c>
       <c r="P10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q10" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R10" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1246,37 +1342,37 @@
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F11" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G11" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11">
         <v>52</v>
       </c>
-      <c r="H11">
-        <v>32</v>
-      </c>
       <c r="I11" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J11" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="K11">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="P11" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1290,37 +1386,37 @@
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G12" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H12">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="I12" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="J12" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K12">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="P12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q12" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R12" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1334,37 +1430,19 @@
         <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" t="s">
-        <v>58</v>
-      </c>
-      <c r="H13">
-        <v>39</v>
-      </c>
-      <c r="I13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J13" t="s">
-        <v>59</v>
-      </c>
-      <c r="K13">
-        <v>149</v>
+        <v>44</v>
       </c>
       <c r="P13" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q13" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R13" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1378,37 +1456,19 @@
         <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" t="s">
-        <v>30</v>
-      </c>
-      <c r="G14" t="s">
-        <v>61</v>
-      </c>
-      <c r="H14">
-        <v>28</v>
-      </c>
-      <c r="I14" t="s">
-        <v>32</v>
-      </c>
-      <c r="J14" t="s">
-        <v>62</v>
-      </c>
-      <c r="K14">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="P14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q14" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R14" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1422,37 +1482,37 @@
         <v>20</v>
       </c>
       <c r="D15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15">
+        <v>45</v>
+      </c>
+      <c r="I15" t="s">
+        <v>25</v>
+      </c>
+      <c r="J15" t="s">
         <v>63</v>
       </c>
-      <c r="E15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" t="s">
-        <v>30</v>
-      </c>
-      <c r="G15" t="s">
-        <v>64</v>
-      </c>
-      <c r="H15">
-        <v>27</v>
-      </c>
-      <c r="I15" t="s">
-        <v>47</v>
-      </c>
-      <c r="J15" t="s">
-        <v>65</v>
-      </c>
       <c r="K15">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="P15" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q15" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R15" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1466,19 +1526,37 @@
         <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
         <v>22</v>
       </c>
+      <c r="F16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" t="s">
+        <v>65</v>
+      </c>
+      <c r="H16">
+        <v>31</v>
+      </c>
+      <c r="I16" t="s">
+        <v>25</v>
+      </c>
+      <c r="J16" t="s">
+        <v>66</v>
+      </c>
+      <c r="K16">
+        <v>19</v>
+      </c>
       <c r="P16" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q16" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R16" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -1495,16 +1573,31 @@
         <v>67</v>
       </c>
       <c r="E17" t="s">
-        <v>27</v>
+        <v>31</v>
+      </c>
+      <c r="F17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17">
+        <v>-225</v>
+      </c>
+      <c r="I17" t="s">
+        <v>25</v>
+      </c>
+      <c r="J17" t="s">
+        <v>68</v>
+      </c>
+      <c r="K17">
+        <v>168</v>
       </c>
       <c r="P17" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q17" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R17" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -1518,28 +1611,37 @@
         <v>20</v>
       </c>
       <c r="D18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E18" t="s">
-        <v>29</v>
+        <v>35</v>
+      </c>
+      <c r="F18" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" t="s">
+        <v>70</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="I18" t="s">
+        <v>25</v>
+      </c>
+      <c r="J18" t="s">
+        <v>33</v>
       </c>
       <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="P18" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q18" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R18" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -1553,34 +1655,37 @@
         <v>20</v>
       </c>
       <c r="D19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E19" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F19" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H19">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I19" t="s">
-        <v>32</v>
+        <v>41</v>
+      </c>
+      <c r="J19" t="s">
+        <v>73</v>
       </c>
       <c r="K19">
-        <v>-255</v>
+        <v>-14</v>
       </c>
       <c r="P19" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q19" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R19" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -1594,37 +1699,19 @@
         <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E20" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" t="s">
-        <v>30</v>
-      </c>
-      <c r="G20" t="s">
-        <v>73</v>
-      </c>
-      <c r="H20">
-        <v>47</v>
-      </c>
-      <c r="I20" t="s">
-        <v>32</v>
-      </c>
-      <c r="J20" t="s">
-        <v>74</v>
-      </c>
-      <c r="K20">
-        <v>148</v>
+        <v>44</v>
       </c>
       <c r="P20" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q20" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R20" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -1641,34 +1728,16 @@
         <v>75</v>
       </c>
       <c r="E21" t="s">
-        <v>41</v>
-      </c>
-      <c r="F21" t="s">
-        <v>30</v>
-      </c>
-      <c r="G21" t="s">
-        <v>31</v>
-      </c>
-      <c r="H21">
-        <v>52</v>
-      </c>
-      <c r="I21" t="s">
-        <v>32</v>
-      </c>
-      <c r="J21" t="s">
-        <v>76</v>
-      </c>
-      <c r="K21">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="P21" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q21" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R21" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -1682,34 +1751,37 @@
         <v>20</v>
       </c>
       <c r="D22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" t="s">
         <v>77</v>
       </c>
-      <c r="E22" t="s">
-        <v>45</v>
-      </c>
-      <c r="F22" t="s">
-        <v>30</v>
-      </c>
-      <c r="G22" t="s">
+      <c r="H22">
+        <v>67</v>
+      </c>
+      <c r="I22" t="s">
+        <v>25</v>
+      </c>
+      <c r="J22" t="s">
         <v>78</v>
       </c>
-      <c r="H22">
-        <v>45</v>
-      </c>
-      <c r="I22" t="s">
-        <v>47</v>
-      </c>
       <c r="K22">
-        <v>-255</v>
+        <v>29</v>
       </c>
       <c r="P22" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q22" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R22" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -1728,14 +1800,32 @@
       <c r="E23" t="s">
         <v>22</v>
       </c>
+      <c r="F23" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H23">
+        <v>43</v>
+      </c>
+      <c r="I23" t="s">
+        <v>25</v>
+      </c>
+      <c r="J23" t="s">
+        <v>81</v>
+      </c>
+      <c r="K23">
+        <v>46</v>
+      </c>
       <c r="P23" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q23" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R23" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -1749,19 +1839,37 @@
         <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E24" t="s">
-        <v>27</v>
+        <v>31</v>
+      </c>
+      <c r="F24" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" t="s">
+        <v>83</v>
+      </c>
+      <c r="H24">
+        <v>66</v>
+      </c>
+      <c r="I24" t="s">
+        <v>25</v>
+      </c>
+      <c r="J24" t="s">
+        <v>84</v>
+      </c>
+      <c r="K24">
+        <v>122</v>
       </c>
       <c r="P24" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q24" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R24" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -1775,37 +1883,37 @@
         <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E25" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F25" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G25" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="H25">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="I25" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K25">
         <v>31</v>
       </c>
       <c r="P25" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q25" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R25" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -1819,28 +1927,37 @@
         <v>20</v>
       </c>
       <c r="D26" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E26" t="s">
-        <v>35</v>
+        <v>39</v>
+      </c>
+      <c r="F26" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" t="s">
+        <v>88</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c r="I26" t="s">
+        <v>41</v>
+      </c>
+      <c r="J26" t="s">
+        <v>89</v>
       </c>
       <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26" t="s">
-        <v>85</v>
+        <v>177</v>
       </c>
       <c r="P26" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q26" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R26" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -1854,37 +1971,19 @@
         <v>20</v>
       </c>
       <c r="D27" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E27" t="s">
-        <v>38</v>
-      </c>
-      <c r="F27" t="s">
-        <v>30</v>
-      </c>
-      <c r="G27" t="s">
-        <v>46</v>
-      </c>
-      <c r="H27">
-        <v>36</v>
-      </c>
-      <c r="I27" t="s">
-        <v>32</v>
-      </c>
-      <c r="J27" t="s">
-        <v>87</v>
-      </c>
-      <c r="K27">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="P27" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q27" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R27" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -1898,37 +1997,19 @@
         <v>20</v>
       </c>
       <c r="D28" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E28" t="s">
-        <v>41</v>
-      </c>
-      <c r="F28" t="s">
-        <v>30</v>
-      </c>
-      <c r="G28" t="s">
-        <v>61</v>
-      </c>
-      <c r="H28">
-        <v>28</v>
-      </c>
-      <c r="I28" t="s">
-        <v>32</v>
-      </c>
-      <c r="J28" t="s">
-        <v>89</v>
-      </c>
-      <c r="K28">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="P28" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q28" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R28" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -1942,37 +2023,37 @@
         <v>20</v>
       </c>
       <c r="D29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E29" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" t="s">
+        <v>23</v>
+      </c>
+      <c r="G29" t="s">
+        <v>40</v>
+      </c>
+      <c r="H29">
         <v>45</v>
       </c>
-      <c r="F29" t="s">
-        <v>30</v>
-      </c>
-      <c r="G29" t="s">
-        <v>91</v>
-      </c>
-      <c r="H29">
-        <v>31</v>
-      </c>
       <c r="I29" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="J29" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K29">
-        <v>-19</v>
+        <v>42</v>
       </c>
       <c r="P29" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q29" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R29" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -1986,19 +2067,37 @@
         <v>20</v>
       </c>
       <c r="D30" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E30" t="s">
         <v>22</v>
       </c>
+      <c r="F30" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30" t="s">
+        <v>95</v>
+      </c>
+      <c r="H30">
+        <v>71</v>
+      </c>
+      <c r="I30" t="s">
+        <v>25</v>
+      </c>
+      <c r="J30" t="s">
+        <v>96</v>
+      </c>
+      <c r="K30">
+        <v>5</v>
+      </c>
       <c r="P30" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q30" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R30" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -2012,3531 +2111,3559 @@
         <v>20</v>
       </c>
       <c r="D31" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E31" t="s">
-        <v>27</v>
+        <v>31</v>
+      </c>
+      <c r="F31" t="s">
+        <v>23</v>
+      </c>
+      <c r="G31" t="s">
+        <v>72</v>
+      </c>
+      <c r="H31">
+        <v>54</v>
+      </c>
+      <c r="I31" t="s">
+        <v>25</v>
+      </c>
+      <c r="J31" t="s">
+        <v>98</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q31" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R31" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:18">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="B32" t="s">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
         <v>20</v>
       </c>
       <c r="D32" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="E32" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F32" t="s">
-        <v>30</v>
-      </c>
-      <c r="G32" t="s">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="H32">
-        <v>50</v>
+        <v>-225</v>
       </c>
       <c r="I32" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J32" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K32">
-        <v>52</v>
+        <v>-4</v>
       </c>
       <c r="P32" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q32" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R32" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:18">
       <c r="A33" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C33" t="s">
         <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E33" t="s">
-        <v>22</v>
+        <v>31</v>
+      </c>
+      <c r="F33" t="s">
+        <v>23</v>
+      </c>
+      <c r="G33" t="s">
+        <v>102</v>
+      </c>
+      <c r="H33">
+        <v>3</v>
+      </c>
+      <c r="I33" t="s">
+        <v>25</v>
+      </c>
+      <c r="J33" t="s">
+        <v>103</v>
+      </c>
+      <c r="K33">
+        <v>264</v>
       </c>
       <c r="P33" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q33" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R33" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:18">
       <c r="A34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
         <v>20</v>
       </c>
       <c r="D34" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E34" t="s">
-        <v>27</v>
+        <v>35</v>
+      </c>
+      <c r="F34" t="s">
+        <v>23</v>
+      </c>
+      <c r="G34" t="s">
+        <v>104</v>
+      </c>
+      <c r="H34">
+        <v>5</v>
+      </c>
+      <c r="I34" t="s">
+        <v>25</v>
+      </c>
+      <c r="J34" t="s">
+        <v>105</v>
+      </c>
+      <c r="K34">
+        <v>15</v>
       </c>
       <c r="P34" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q34" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R34" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:18">
       <c r="A35" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C35" t="s">
         <v>20</v>
       </c>
       <c r="D35" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E35" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F35" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G35" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H35">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I35" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="J35" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="K35">
-        <v>-28</v>
+        <v>188</v>
       </c>
       <c r="P35" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q35" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R35" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="1:18">
       <c r="A36" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B36" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C36" t="s">
         <v>20</v>
       </c>
       <c r="D36" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E36" t="s">
-        <v>35</v>
-      </c>
-      <c r="F36" t="s">
-        <v>30</v>
-      </c>
-      <c r="G36" t="s">
-        <v>102</v>
-      </c>
-      <c r="H36">
-        <v>9</v>
-      </c>
-      <c r="I36" t="s">
-        <v>32</v>
-      </c>
-      <c r="K36">
-        <v>-255</v>
+        <v>44</v>
       </c>
       <c r="P36" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q36" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R36" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="1:18">
       <c r="A37" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B37" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
         <v>20</v>
       </c>
       <c r="D37" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E37" t="s">
-        <v>38</v>
-      </c>
-      <c r="F37" t="s">
-        <v>30</v>
-      </c>
-      <c r="G37" t="s">
-        <v>103</v>
-      </c>
-      <c r="H37">
-        <v>-6</v>
-      </c>
-      <c r="I37" t="s">
-        <v>32</v>
-      </c>
-      <c r="J37" t="s">
-        <v>104</v>
-      </c>
-      <c r="K37">
-        <v>343</v>
+        <v>46</v>
       </c>
       <c r="P37" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q37" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R37" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38" spans="1:18">
       <c r="A38" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B38" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C38" t="s">
         <v>20</v>
       </c>
       <c r="D38" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E38" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F38" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G38" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H38">
-        <v>-2</v>
+        <v>17</v>
       </c>
       <c r="I38" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J38" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K38">
-        <v>103</v>
+        <v>191</v>
       </c>
       <c r="P38" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q38" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R38" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39" spans="1:18">
       <c r="A39" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B39" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C39" t="s">
         <v>20</v>
       </c>
       <c r="D39" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E39" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F39" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G39" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="H39">
-        <v>-6</v>
+        <v>15</v>
       </c>
       <c r="I39" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="J39" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K39">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="P39" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q39" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R39" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="1:18">
       <c r="A40" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B40" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C40" t="s">
         <v>20</v>
       </c>
       <c r="D40" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E40" t="s">
-        <v>22</v>
+        <v>31</v>
+      </c>
+      <c r="F40" t="s">
+        <v>23</v>
+      </c>
+      <c r="G40" t="s">
+        <v>112</v>
+      </c>
+      <c r="H40">
+        <v>-6</v>
+      </c>
+      <c r="I40" t="s">
+        <v>25</v>
+      </c>
+      <c r="J40" t="s">
+        <v>113</v>
+      </c>
+      <c r="K40">
+        <v>-19</v>
       </c>
       <c r="P40" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q40" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R40" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41" spans="1:18">
       <c r="A41" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B41" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C41" t="s">
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E41" t="s">
-        <v>27</v>
+        <v>35</v>
+      </c>
+      <c r="F41" t="s">
+        <v>23</v>
+      </c>
+      <c r="G41" t="s">
+        <v>108</v>
+      </c>
+      <c r="H41">
+        <v>17</v>
+      </c>
+      <c r="I41" t="s">
+        <v>25</v>
+      </c>
+      <c r="J41" t="s">
+        <v>114</v>
+      </c>
+      <c r="K41">
+        <v>215</v>
       </c>
       <c r="P41" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q41" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R41" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42" spans="1:18">
       <c r="A42" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B42" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C42" t="s">
         <v>20</v>
       </c>
       <c r="D42" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E42" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F42" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G42" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="H42">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I42" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="J42" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K42">
-        <v>169</v>
+        <v>52</v>
       </c>
       <c r="P42" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q42" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R42" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:18">
       <c r="A43" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B43" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C43" t="s">
         <v>20</v>
       </c>
       <c r="D43" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E43" t="s">
-        <v>35</v>
-      </c>
-      <c r="F43" t="s">
-        <v>30</v>
-      </c>
-      <c r="G43" t="s">
-        <v>110</v>
-      </c>
-      <c r="H43">
-        <v>-5</v>
-      </c>
-      <c r="I43" t="s">
-        <v>32</v>
-      </c>
-      <c r="J43" t="s">
-        <v>111</v>
-      </c>
-      <c r="K43">
-        <v>279</v>
+        <v>44</v>
       </c>
       <c r="P43" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q43" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R43" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44" spans="1:18">
       <c r="A44" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B44" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C44" t="s">
         <v>20</v>
       </c>
       <c r="D44" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E44" t="s">
-        <v>38</v>
-      </c>
-      <c r="F44" t="s">
-        <v>30</v>
-      </c>
-      <c r="G44" t="s">
-        <v>112</v>
-      </c>
-      <c r="H44">
-        <v>-24</v>
-      </c>
-      <c r="I44" t="s">
-        <v>32</v>
-      </c>
-      <c r="K44">
-        <v>-255</v>
+        <v>46</v>
       </c>
       <c r="P44" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q44" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R44" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="45" spans="1:18">
       <c r="A45" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C45" t="s">
         <v>20</v>
       </c>
       <c r="D45" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E45" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F45" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G45" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="H45">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="I45" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J45" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="K45">
-        <v>124</v>
+        <v>255</v>
       </c>
       <c r="P45" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q45" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R45" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46" spans="1:18">
       <c r="A46" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B46" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C46" t="s">
         <v>20</v>
       </c>
       <c r="D46" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E46" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F46" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G46" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H46">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I46" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="J46" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="K46">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="P46" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q46" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R46" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47" spans="1:18">
       <c r="A47" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B47" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C47" t="s">
         <v>20</v>
       </c>
       <c r="D47" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E47" t="s">
-        <v>22</v>
+        <v>31</v>
+      </c>
+      <c r="F47" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47" t="s">
+        <v>121</v>
+      </c>
+      <c r="H47">
+        <v>-24</v>
+      </c>
+      <c r="I47" t="s">
+        <v>25</v>
+      </c>
+      <c r="J47" t="s">
+        <v>122</v>
+      </c>
+      <c r="K47">
+        <v>144</v>
       </c>
       <c r="P47" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q47" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R47" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:18">
       <c r="A48" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B48" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C48" t="s">
         <v>20</v>
       </c>
       <c r="D48" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E48" t="s">
-        <v>27</v>
+        <v>35</v>
+      </c>
+      <c r="F48" t="s">
+        <v>23</v>
+      </c>
+      <c r="G48" t="s">
+        <v>123</v>
+      </c>
+      <c r="H48">
+        <v>16</v>
+      </c>
+      <c r="I48" t="s">
+        <v>25</v>
+      </c>
+      <c r="J48" t="s">
+        <v>124</v>
+      </c>
+      <c r="K48">
+        <v>200</v>
       </c>
       <c r="P48" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q48" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R48" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49" spans="1:18">
       <c r="A49" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B49" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C49" t="s">
         <v>20</v>
       </c>
       <c r="D49" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E49" t="s">
-        <v>29</v>
+        <v>39</v>
+      </c>
+      <c r="F49" t="s">
+        <v>23</v>
+      </c>
+      <c r="G49" t="s">
+        <v>125</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>26</v>
+      </c>
+      <c r="I49" t="s">
+        <v>41</v>
+      </c>
+      <c r="J49" t="s">
+        <v>126</v>
       </c>
       <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="P49" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q49" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R49" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50" spans="1:18">
       <c r="A50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C50" t="s">
         <v>20</v>
       </c>
       <c r="D50" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E50" t="s">
-        <v>35</v>
-      </c>
-      <c r="F50" t="s">
-        <v>30</v>
-      </c>
-      <c r="G50" t="s">
-        <v>117</v>
-      </c>
-      <c r="H50">
-        <v>5</v>
-      </c>
-      <c r="I50" t="s">
-        <v>32</v>
-      </c>
-      <c r="J50" t="s">
-        <v>118</v>
-      </c>
-      <c r="K50">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="P50" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q50" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R50" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51" spans="1:18">
       <c r="A51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B51" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C51" t="s">
         <v>20</v>
       </c>
       <c r="D51" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E51" t="s">
-        <v>38</v>
-      </c>
-      <c r="F51" t="s">
-        <v>30</v>
-      </c>
-      <c r="G51" t="s">
-        <v>119</v>
-      </c>
-      <c r="H51">
-        <v>-16</v>
-      </c>
-      <c r="I51" t="s">
-        <v>32</v>
-      </c>
-      <c r="J51" t="s">
-        <v>120</v>
-      </c>
-      <c r="K51">
-        <v>233</v>
+        <v>46</v>
       </c>
       <c r="P51" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q51" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R51" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="52" spans="1:18">
       <c r="A52" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B52" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C52" t="s">
         <v>20</v>
       </c>
       <c r="D52" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E52" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F52" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G52" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="H52">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I52" t="s">
-        <v>32</v>
+        <v>25</v>
+      </c>
+      <c r="J52" t="s">
+        <v>109</v>
       </c>
       <c r="K52">
-        <v>-255</v>
+        <v>191</v>
       </c>
       <c r="P52" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q52" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R52" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="53" spans="1:18">
       <c r="A53" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B53" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C53" t="s">
         <v>20</v>
       </c>
       <c r="D53" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E53" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F53" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G53" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="H53">
-        <v>-2</v>
+        <v>75</v>
       </c>
       <c r="I53" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="J53" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="K53">
-        <v>62</v>
+        <v>137</v>
       </c>
       <c r="P53" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q53" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R53" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="54" spans="1:18">
       <c r="A54" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B54" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C54" t="s">
         <v>20</v>
       </c>
       <c r="D54" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E54" t="s">
+        <v>31</v>
+      </c>
+      <c r="F54" t="s">
+        <v>23</v>
+      </c>
+      <c r="G54" t="s">
+        <v>130</v>
+      </c>
+      <c r="H54">
         <v>22</v>
       </c>
+      <c r="I54" t="s">
+        <v>25</v>
+      </c>
+      <c r="J54" t="s">
+        <v>131</v>
+      </c>
+      <c r="K54">
+        <v>194</v>
+      </c>
       <c r="P54" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q54" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R54" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="55" spans="1:18">
       <c r="A55" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B55" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C55" t="s">
         <v>20</v>
       </c>
       <c r="D55" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E55" t="s">
-        <v>27</v>
+        <v>35</v>
+      </c>
+      <c r="F55" t="s">
+        <v>23</v>
+      </c>
+      <c r="G55" t="s">
+        <v>132</v>
+      </c>
+      <c r="H55">
+        <v>4</v>
+      </c>
+      <c r="I55" t="s">
+        <v>25</v>
+      </c>
+      <c r="J55" t="s">
+        <v>133</v>
+      </c>
+      <c r="K55">
+        <v>-20</v>
       </c>
       <c r="P55" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q55" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R55" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="56" spans="1:18">
       <c r="A56" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B56" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C56" t="s">
         <v>20</v>
       </c>
       <c r="D56" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E56" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F56" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G56" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="H56">
-        <v>-12</v>
+        <v>49</v>
       </c>
       <c r="I56" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="K56">
         <v>-255</v>
       </c>
       <c r="P56" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q56" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R56" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="57" spans="1:18">
       <c r="A57" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B57" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C57" t="s">
         <v>20</v>
       </c>
       <c r="D57" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E57" t="s">
-        <v>35</v>
-      </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
-      <c r="K57">
-        <v>0</v>
-      </c>
-      <c r="L57" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="P57" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q57" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R57" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="58" spans="1:18">
       <c r="A58" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B58" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C58" t="s">
         <v>20</v>
       </c>
       <c r="D58" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E58" t="s">
-        <v>38</v>
-      </c>
-      <c r="F58" t="s">
-        <v>30</v>
-      </c>
-      <c r="G58" t="s">
-        <v>30</v>
-      </c>
-      <c r="H58">
-        <v>0</v>
-      </c>
-      <c r="I58" t="s">
-        <v>32</v>
-      </c>
-      <c r="J58" t="s">
-        <v>124</v>
-      </c>
-      <c r="K58">
-        <v>336</v>
+        <v>46</v>
       </c>
       <c r="P58" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q58" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R58" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="59" spans="1:18">
       <c r="A59" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B59" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C59" t="s">
         <v>20</v>
       </c>
       <c r="D59" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E59" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F59" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G59" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="H59">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J59" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="K59">
-        <v>239</v>
+        <v>192</v>
       </c>
       <c r="P59" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q59" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R59" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="60" spans="1:18">
       <c r="A60" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B60" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C60" t="s">
         <v>20</v>
       </c>
       <c r="D60" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E60" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F60" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G60" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="H60">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="I60" t="s">
-        <v>47</v>
+        <v>25</v>
+      </c>
+      <c r="J60" t="s">
+        <v>137</v>
       </c>
       <c r="K60">
-        <v>-255</v>
+        <v>196</v>
       </c>
       <c r="P60" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q60" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R60" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="61" spans="1:18">
       <c r="A61" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B61" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C61" t="s">
         <v>20</v>
       </c>
       <c r="D61" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E61" t="s">
-        <v>22</v>
+        <v>31</v>
+      </c>
+      <c r="F61" t="s">
+        <v>23</v>
+      </c>
+      <c r="G61" t="s">
+        <v>135</v>
+      </c>
+      <c r="H61">
+        <v>1</v>
+      </c>
+      <c r="I61" t="s">
+        <v>25</v>
+      </c>
+      <c r="J61" t="s">
+        <v>138</v>
+      </c>
+      <c r="K61">
+        <v>120</v>
       </c>
       <c r="P61" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q61" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R61" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="62" spans="1:18">
       <c r="A62" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="B62" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="C62" t="s">
         <v>20</v>
       </c>
       <c r="D62" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="E62" t="s">
-        <v>27</v>
+        <v>22</v>
+      </c>
+      <c r="F62" t="s">
+        <v>23</v>
+      </c>
+      <c r="G62" t="s">
+        <v>141</v>
+      </c>
+      <c r="H62">
+        <v>25</v>
+      </c>
+      <c r="I62" t="s">
+        <v>25</v>
+      </c>
+      <c r="J62" t="s">
+        <v>142</v>
+      </c>
+      <c r="K62">
+        <v>8</v>
       </c>
       <c r="P62" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q62" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R62" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="63" spans="1:18">
       <c r="A63" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="B63" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="C63" t="s">
         <v>20</v>
       </c>
       <c r="D63" t="s">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="E63" t="s">
-        <v>29</v>
-      </c>
-      <c r="O63" t="s">
-        <v>127</v>
+        <v>31</v>
+      </c>
+      <c r="F63" t="s">
+        <v>23</v>
+      </c>
+      <c r="G63" t="s">
+        <v>130</v>
+      </c>
+      <c r="H63">
+        <v>22</v>
+      </c>
+      <c r="I63" t="s">
+        <v>25</v>
+      </c>
+      <c r="J63" t="s">
+        <v>52</v>
+      </c>
+      <c r="K63">
+        <v>40</v>
       </c>
       <c r="P63" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q63" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R63" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="64" spans="1:18">
       <c r="A64" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B64" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C64" t="s">
         <v>20</v>
       </c>
       <c r="D64" t="s">
+        <v>34</v>
+      </c>
+      <c r="E64" t="s">
+        <v>35</v>
+      </c>
+      <c r="F64" t="s">
+        <v>23</v>
+      </c>
+      <c r="G64" t="s">
+        <v>143</v>
+      </c>
+      <c r="H64">
         <v>21</v>
       </c>
-      <c r="E64" t="s">
-        <v>22</v>
+      <c r="I64" t="s">
+        <v>25</v>
+      </c>
+      <c r="J64" t="s">
+        <v>144</v>
+      </c>
+      <c r="K64">
+        <v>14</v>
       </c>
       <c r="P64" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q64" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R64" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="65" spans="1:18">
       <c r="A65" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B65" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C65" t="s">
         <v>20</v>
       </c>
       <c r="D65" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E65" t="s">
-        <v>27</v>
+        <v>39</v>
+      </c>
+      <c r="F65" t="s">
+        <v>23</v>
+      </c>
+      <c r="G65" t="s">
+        <v>145</v>
+      </c>
+      <c r="H65">
+        <v>20</v>
+      </c>
+      <c r="I65" t="s">
+        <v>41</v>
+      </c>
+      <c r="J65" t="s">
+        <v>146</v>
+      </c>
+      <c r="K65">
+        <v>43</v>
       </c>
       <c r="P65" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q65" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R65" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="66" spans="1:18">
       <c r="A66" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B66" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C66" t="s">
         <v>20</v>
       </c>
       <c r="D66" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E66" t="s">
-        <v>29</v>
-      </c>
-      <c r="F66" t="s">
-        <v>30</v>
-      </c>
-      <c r="G66" t="s">
-        <v>130</v>
-      </c>
-      <c r="H66">
-        <v>24</v>
-      </c>
-      <c r="I66" t="s">
-        <v>32</v>
-      </c>
-      <c r="J66" t="s">
-        <v>131</v>
-      </c>
-      <c r="K66">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="P66" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q66" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R66" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="67" spans="1:18">
       <c r="A67" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B67" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C67" t="s">
         <v>20</v>
       </c>
       <c r="D67" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="E67" t="s">
-        <v>35</v>
-      </c>
-      <c r="F67" t="s">
-        <v>30</v>
-      </c>
-      <c r="G67" t="s">
-        <v>132</v>
-      </c>
-      <c r="H67">
-        <v>26</v>
-      </c>
-      <c r="I67" t="s">
-        <v>32</v>
-      </c>
-      <c r="J67" t="s">
-        <v>53</v>
-      </c>
-      <c r="K67">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="P67" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q67" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R67" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="68" spans="1:18">
       <c r="A68" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B68" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C68" t="s">
         <v>20</v>
       </c>
       <c r="D68" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E68" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F68" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G68" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="H68">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I68" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J68" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="K68">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="P68" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q68" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R68" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="69" spans="1:18">
       <c r="A69" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B69" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C69" t="s">
         <v>20</v>
       </c>
       <c r="D69" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E69" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="F69" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G69" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="H69">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I69" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J69" t="s">
-        <v>53</v>
+        <v>149</v>
       </c>
       <c r="K69">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="P69" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q69" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R69" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="70" spans="1:18">
       <c r="A70" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B70" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C70" t="s">
         <v>20</v>
       </c>
       <c r="D70" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E70" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="F70" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G70" t="s">
-        <v>61</v>
+        <v>147</v>
       </c>
       <c r="H70">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="J70" t="s">
-        <v>134</v>
+        <v>63</v>
       </c>
       <c r="K70">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="P70" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q70" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R70" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="71" spans="1:18">
       <c r="A71" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B71" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C71" t="s">
         <v>20</v>
       </c>
       <c r="D71" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E71" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="F71" t="s">
+        <v>23</v>
+      </c>
+      <c r="G71" t="s">
+        <v>150</v>
+      </c>
+      <c r="H71">
+        <v>19</v>
+      </c>
+      <c r="I71" t="s">
+        <v>25</v>
+      </c>
+      <c r="J71" t="s">
+        <v>151</v>
+      </c>
+      <c r="K71">
+        <v>44</v>
       </c>
       <c r="P71" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q71" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R71" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="72" spans="1:18">
       <c r="A72" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B72" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C72" t="s">
         <v>20</v>
       </c>
       <c r="D72" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E72" t="s">
-        <v>27</v>
+        <v>39</v>
+      </c>
+      <c r="F72" t="s">
+        <v>23</v>
+      </c>
+      <c r="G72" t="s">
+        <v>110</v>
+      </c>
+      <c r="H72">
+        <v>15</v>
+      </c>
+      <c r="I72" t="s">
+        <v>41</v>
+      </c>
+      <c r="J72" t="s">
+        <v>152</v>
+      </c>
+      <c r="K72">
+        <v>9</v>
       </c>
       <c r="P72" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q72" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R72" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="73" spans="1:18">
       <c r="A73" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B73" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C73" t="s">
         <v>20</v>
       </c>
       <c r="D73" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E73" t="s">
-        <v>29</v>
-      </c>
-      <c r="F73" t="s">
-        <v>30</v>
-      </c>
-      <c r="G73" t="s">
-        <v>135</v>
-      </c>
-      <c r="H73">
-        <v>17</v>
-      </c>
-      <c r="I73" t="s">
-        <v>32</v>
-      </c>
-      <c r="J73" t="s">
-        <v>136</v>
-      </c>
-      <c r="K73">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="P73" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q73" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R73" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74" spans="1:18">
       <c r="A74" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B74" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C74" t="s">
         <v>20</v>
       </c>
       <c r="D74" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E74" t="s">
-        <v>35</v>
-      </c>
-      <c r="F74" t="s">
-        <v>30</v>
-      </c>
-      <c r="G74" t="s">
-        <v>137</v>
-      </c>
-      <c r="H74">
-        <v>11</v>
-      </c>
-      <c r="I74" t="s">
-        <v>32</v>
-      </c>
-      <c r="J74" t="s">
-        <v>138</v>
-      </c>
-      <c r="K74">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="P74" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q74" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R74" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="75" spans="1:18">
       <c r="A75" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B75" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C75" t="s">
         <v>20</v>
       </c>
       <c r="D75" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E75" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F75" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G75" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="H75">
         <v>23</v>
       </c>
       <c r="I75" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J75" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="K75">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="P75" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q75" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R75" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="76" spans="1:18">
       <c r="A76" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B76" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C76" t="s">
         <v>20</v>
       </c>
       <c r="D76" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E76" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="F76" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G76" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="H76">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I76" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J76" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="K76">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="P76" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q76" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R76" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="77" spans="1:18">
       <c r="A77" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B77" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C77" t="s">
         <v>20</v>
       </c>
       <c r="D77" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E77" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="F77" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G77" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="H77">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I77" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="J77" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="K77">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="P77" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q77" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R77" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78" spans="1:18">
       <c r="A78" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B78" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C78" t="s">
         <v>20</v>
       </c>
       <c r="D78" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E78" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="F78" t="s">
+        <v>23</v>
+      </c>
+      <c r="G78" t="s">
+        <v>110</v>
+      </c>
+      <c r="H78">
+        <v>15</v>
+      </c>
+      <c r="I78" t="s">
+        <v>25</v>
+      </c>
+      <c r="J78" t="s">
+        <v>157</v>
+      </c>
+      <c r="K78">
+        <v>357</v>
       </c>
       <c r="P78" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q78" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R78" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="79" spans="1:18">
       <c r="A79" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B79" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C79" t="s">
         <v>20</v>
       </c>
       <c r="D79" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E79" t="s">
-        <v>27</v>
+        <v>39</v>
+      </c>
+      <c r="F79" t="s">
+        <v>23</v>
+      </c>
+      <c r="G79" t="s">
+        <v>125</v>
+      </c>
+      <c r="H79">
+        <v>26</v>
+      </c>
+      <c r="I79" t="s">
+        <v>41</v>
+      </c>
+      <c r="J79" t="s">
+        <v>158</v>
+      </c>
+      <c r="K79">
+        <v>32</v>
       </c>
       <c r="P79" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q79" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R79" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="80" spans="1:18">
       <c r="A80" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B80" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C80" t="s">
         <v>20</v>
       </c>
       <c r="D80" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E80" t="s">
-        <v>29</v>
-      </c>
-      <c r="H80">
-        <v>0</v>
-      </c>
-      <c r="K80">
-        <v>0</v>
-      </c>
-      <c r="L80" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="P80" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q80" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R80" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="81" spans="1:18">
       <c r="A81" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B81" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C81" t="s">
         <v>20</v>
       </c>
       <c r="D81" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E81" t="s">
-        <v>35</v>
-      </c>
-      <c r="F81" t="s">
-        <v>30</v>
-      </c>
-      <c r="G81" t="s">
-        <v>143</v>
-      </c>
-      <c r="H81">
-        <v>33</v>
-      </c>
-      <c r="I81" t="s">
-        <v>32</v>
-      </c>
-      <c r="J81" t="s">
-        <v>144</v>
-      </c>
-      <c r="K81">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="P81" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q81" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R81" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="82" spans="1:18">
       <c r="A82" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B82" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C82" t="s">
         <v>20</v>
       </c>
       <c r="D82" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E82" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F82" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G82" t="s">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="H82">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I82" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J82" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="K82">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="P82" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q82" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R82" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="83" spans="1:18">
       <c r="A83" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B83" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C83" t="s">
         <v>20</v>
       </c>
       <c r="D83" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E83" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="F83" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G83" t="s">
-        <v>55</v>
+        <v>143</v>
       </c>
       <c r="H83">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I83" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J83" t="s">
-        <v>146</v>
+        <v>52</v>
       </c>
       <c r="K83">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="P83" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q83" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R83" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="84" spans="1:18">
       <c r="A84" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B84" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C84" t="s">
         <v>20</v>
       </c>
       <c r="D84" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E84" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="F84" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G84" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="H84">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I84" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="J84" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="K84">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="P84" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q84" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R84" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="85" spans="1:18">
       <c r="A85" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B85" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C85" t="s">
         <v>20</v>
       </c>
       <c r="D85" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E85" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="F85" t="s">
+        <v>23</v>
+      </c>
+      <c r="G85" t="s">
+        <v>143</v>
+      </c>
+      <c r="H85">
+        <v>21</v>
+      </c>
+      <c r="I85" t="s">
+        <v>25</v>
+      </c>
+      <c r="J85" t="s">
+        <v>161</v>
+      </c>
+      <c r="K85">
+        <v>11</v>
       </c>
       <c r="P85" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q85" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R85" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="86" spans="1:18">
       <c r="A86" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B86" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C86" t="s">
         <v>20</v>
       </c>
       <c r="D86" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="E86" t="s">
-        <v>27</v>
+        <v>39</v>
+      </c>
+      <c r="F86" t="s">
+        <v>23</v>
+      </c>
+      <c r="G86" t="s">
+        <v>153</v>
+      </c>
+      <c r="H86">
+        <v>23</v>
+      </c>
+      <c r="I86" t="s">
+        <v>41</v>
+      </c>
+      <c r="J86" t="s">
+        <v>162</v>
+      </c>
+      <c r="K86">
+        <v>49</v>
       </c>
       <c r="P86" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q86" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R86" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="87" spans="1:18">
       <c r="A87" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B87" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C87" t="s">
         <v>20</v>
       </c>
       <c r="D87" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="E87" t="s">
-        <v>29</v>
-      </c>
-      <c r="F87" t="s">
-        <v>30</v>
-      </c>
-      <c r="G87" t="s">
-        <v>91</v>
-      </c>
-      <c r="H87">
-        <v>31</v>
-      </c>
-      <c r="I87" t="s">
-        <v>32</v>
-      </c>
-      <c r="J87" t="s">
-        <v>43</v>
-      </c>
-      <c r="K87">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="P87" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q87" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R87" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="88" spans="1:18">
       <c r="A88" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B88" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C88" t="s">
         <v>20</v>
       </c>
       <c r="D88" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E88" t="s">
-        <v>35</v>
-      </c>
-      <c r="H88">
-        <v>0</v>
-      </c>
-      <c r="K88">
-        <v>0</v>
-      </c>
-      <c r="L88" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="P88" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q88" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R88" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="89" spans="1:18">
       <c r="A89" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B89" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C89" t="s">
         <v>20</v>
       </c>
       <c r="D89" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E89" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F89" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G89" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="H89">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I89" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J89" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
       <c r="K89">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="P89" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q89" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R89" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="90" spans="1:18">
       <c r="A90" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B90" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C90" t="s">
         <v>20</v>
       </c>
       <c r="D90" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E90" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="F90" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G90" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="H90">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I90" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J90" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="K90">
-        <v>306</v>
+        <v>12</v>
       </c>
       <c r="P90" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q90" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R90" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="91" spans="1:18">
       <c r="A91" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B91" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C91" t="s">
         <v>20</v>
       </c>
       <c r="D91" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E91" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="F91" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G91" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="H91">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I91" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="J91" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K91">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="P91" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q91" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R91" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="92" spans="1:18">
       <c r="A92" t="s">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="B92" t="s">
-        <v>129</v>
+        <v>165</v>
       </c>
       <c r="C92" t="s">
         <v>20</v>
       </c>
       <c r="D92" t="s">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="E92" t="s">
         <v>22</v>
       </c>
+      <c r="F92" t="s">
+        <v>23</v>
+      </c>
+      <c r="G92" t="s">
+        <v>150</v>
+      </c>
+      <c r="H92">
+        <v>19</v>
+      </c>
+      <c r="I92" t="s">
+        <v>25</v>
+      </c>
+      <c r="J92" t="s">
+        <v>166</v>
+      </c>
+      <c r="K92">
+        <v>77</v>
+      </c>
       <c r="P92" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q92" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R92" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="93" spans="1:18">
       <c r="A93" t="s">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="B93" t="s">
-        <v>129</v>
+        <v>165</v>
       </c>
       <c r="C93" t="s">
         <v>20</v>
       </c>
       <c r="D93" t="s">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="E93" t="s">
-        <v>27</v>
+        <v>31</v>
+      </c>
+      <c r="F93" t="s">
+        <v>23</v>
+      </c>
+      <c r="G93" t="s">
+        <v>145</v>
+      </c>
+      <c r="H93">
+        <v>20</v>
+      </c>
+      <c r="I93" t="s">
+        <v>25</v>
+      </c>
+      <c r="J93" t="s">
+        <v>167</v>
+      </c>
+      <c r="K93">
+        <v>43</v>
       </c>
       <c r="P93" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q93" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R93" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="94" spans="1:18">
       <c r="A94" t="s">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="B94" t="s">
-        <v>129</v>
+        <v>165</v>
       </c>
       <c r="C94" t="s">
         <v>20</v>
       </c>
       <c r="D94" t="s">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="E94" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F94" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G94" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="H94">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I94" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J94" t="s">
-        <v>62</v>
+        <v>168</v>
       </c>
       <c r="K94">
-        <v>17</v>
+        <v>135</v>
       </c>
       <c r="P94" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q94" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R94" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="95" spans="1:18">
       <c r="A95" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B95" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C95" t="s">
         <v>20</v>
       </c>
       <c r="D95" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="E95" t="s">
-        <v>22</v>
+        <v>39</v>
+      </c>
+      <c r="F95" t="s">
+        <v>23</v>
+      </c>
+      <c r="G95" t="s">
+        <v>169</v>
+      </c>
+      <c r="H95">
+        <v>13</v>
+      </c>
+      <c r="I95" t="s">
+        <v>41</v>
+      </c>
+      <c r="J95" t="s">
+        <v>170</v>
+      </c>
+      <c r="K95">
+        <v>88</v>
       </c>
       <c r="P95" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q95" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R95" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="96" spans="1:18">
       <c r="A96" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B96" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C96" t="s">
         <v>20</v>
       </c>
       <c r="D96" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E96" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="P96" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q96" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R96" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="97" spans="1:18">
       <c r="A97" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B97" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C97" t="s">
         <v>20</v>
       </c>
       <c r="D97" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E97" t="s">
-        <v>29</v>
-      </c>
-      <c r="F97" t="s">
-        <v>30</v>
-      </c>
-      <c r="G97" t="s">
-        <v>133</v>
-      </c>
-      <c r="H97">
-        <v>21</v>
-      </c>
-      <c r="I97" t="s">
-        <v>32</v>
-      </c>
-      <c r="J97" t="s">
-        <v>48</v>
-      </c>
-      <c r="K97">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="P97" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q97" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R97" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="98" spans="1:18">
       <c r="A98" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B98" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C98" t="s">
         <v>20</v>
       </c>
       <c r="D98" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="E98" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="F98" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G98" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="H98">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="I98" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J98" t="s">
-        <v>153</v>
+        <v>25</v>
       </c>
       <c r="K98">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="P98" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q98" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R98" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="99" spans="1:18">
       <c r="A99" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B99" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C99" t="s">
         <v>20</v>
       </c>
       <c r="D99" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="E99" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F99" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G99" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="H99">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I99" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J99" t="s">
-        <v>48</v>
+        <v>172</v>
       </c>
       <c r="K99">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="P99" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q99" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R99" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="100" spans="1:18">
       <c r="A100" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B100" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C100" t="s">
         <v>20</v>
       </c>
       <c r="D100" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E100" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F100" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G100" t="s">
-        <v>133</v>
+        <v>173</v>
       </c>
       <c r="H100">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I100" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J100" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="K100">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="P100" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q100" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R100" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="101" spans="1:18">
       <c r="A101" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B101" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C101" t="s">
         <v>20</v>
       </c>
       <c r="D101" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E101" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F101" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G101" t="s">
-        <v>55</v>
+        <v>143</v>
       </c>
       <c r="H101">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I101" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="J101" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="K101">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P101" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q101" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R101" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="102" spans="1:18">
       <c r="A102" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B102" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C102" t="s">
         <v>20</v>
       </c>
       <c r="D102" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E102" t="s">
-        <v>22</v>
+        <v>39</v>
+      </c>
+      <c r="F102" t="s">
+        <v>23</v>
+      </c>
+      <c r="G102" t="s">
+        <v>143</v>
+      </c>
+      <c r="H102">
+        <v>21</v>
+      </c>
+      <c r="I102" t="s">
+        <v>41</v>
+      </c>
+      <c r="J102" t="s">
+        <v>176</v>
+      </c>
+      <c r="K102">
+        <v>79</v>
       </c>
       <c r="P102" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q102" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R102" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="103" spans="1:18">
       <c r="A103" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B103" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C103" t="s">
         <v>20</v>
       </c>
       <c r="D103" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E103" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="P103" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q103" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R103" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="104" spans="1:18">
       <c r="A104" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B104" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C104" t="s">
         <v>20</v>
       </c>
       <c r="D104" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E104" t="s">
-        <v>29</v>
-      </c>
-      <c r="F104" t="s">
-        <v>30</v>
-      </c>
-      <c r="G104" t="s">
-        <v>133</v>
-      </c>
-      <c r="H104">
-        <v>21</v>
-      </c>
-      <c r="I104" t="s">
-        <v>32</v>
-      </c>
-      <c r="J104" t="s">
-        <v>156</v>
-      </c>
-      <c r="K104">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="P104" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q104" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R104" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="105" spans="1:18">
       <c r="A105" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B105" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C105" t="s">
         <v>20</v>
       </c>
       <c r="D105" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E105" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="F105" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G105" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="H105">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I105" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J105" t="s">
-        <v>83</v>
+        <v>177</v>
       </c>
       <c r="K105">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="P105" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q105" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R105" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="106" spans="1:18">
       <c r="A106" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B106" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C106" t="s">
         <v>20</v>
       </c>
       <c r="D106" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E106" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F106" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G106" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="H106">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I106" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J106" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="K106">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="P106" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q106" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R106" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="107" spans="1:18">
       <c r="A107" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B107" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C107" t="s">
         <v>20</v>
       </c>
       <c r="D107" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E107" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F107" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G107" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="H107">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I107" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J107" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="K107">
-        <v>9</v>
+        <v>189</v>
       </c>
       <c r="P107" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q107" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R107" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="108" spans="1:18">
       <c r="A108" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B108" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C108" t="s">
         <v>20</v>
       </c>
       <c r="D108" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E108" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F108" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G108" t="s">
-        <v>133</v>
+        <v>173</v>
       </c>
       <c r="H108">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I108" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="J108" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="K108">
-        <v>21</v>
+        <v>290</v>
       </c>
       <c r="P108" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q108" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R108" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="109" spans="1:18">
       <c r="A109" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B109" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C109" t="s">
         <v>20</v>
       </c>
       <c r="D109" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E109" t="s">
-        <v>22</v>
+        <v>39</v>
+      </c>
+      <c r="F109" t="s">
+        <v>23</v>
+      </c>
+      <c r="G109" t="s">
+        <v>135</v>
+      </c>
+      <c r="H109">
+        <v>1</v>
+      </c>
+      <c r="I109" t="s">
+        <v>41</v>
+      </c>
+      <c r="J109" t="s">
+        <v>181</v>
+      </c>
+      <c r="K109">
+        <v>265</v>
       </c>
       <c r="P109" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q109" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R109" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="110" spans="1:18">
       <c r="A110" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B110" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C110" t="s">
         <v>20</v>
       </c>
       <c r="D110" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E110" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="P110" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q110" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R110" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="111" spans="1:18">
       <c r="A111" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B111" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C111" t="s">
         <v>20</v>
       </c>
       <c r="D111" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E111" t="s">
-        <v>29</v>
-      </c>
-      <c r="H111">
-        <v>0</v>
-      </c>
-      <c r="K111">
-        <v>0</v>
-      </c>
-      <c r="L111" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="P111" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q111" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R111" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="112" spans="1:18">
       <c r="A112" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B112" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C112" t="s">
         <v>20</v>
       </c>
       <c r="D112" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E112" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="F112" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G112" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="H112">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I112" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J112" t="s">
-        <v>160</v>
+        <v>37</v>
       </c>
       <c r="K112">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="P112" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q112" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R112" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="113" spans="1:18">
       <c r="A113" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B113" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C113" t="s">
         <v>20</v>
       </c>
       <c r="D113" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E113" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F113" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G113" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="H113">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I113" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J113" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="K113">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="P113" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q113" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R113" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="114" spans="1:18">
       <c r="A114" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B114" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C114" t="s">
         <v>20</v>
       </c>
       <c r="D114" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E114" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F114" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G114" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H114">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I114" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J114" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="K114">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="P114" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q114" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R114" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="115" spans="1:18">
       <c r="A115" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B115" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C115" t="s">
         <v>20</v>
       </c>
       <c r="D115" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E115" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F115" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G115" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="H115">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I115" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="J115" t="s">
-        <v>56</v>
+        <v>184</v>
       </c>
       <c r="K115">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="P115" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q115" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R115" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="116" spans="1:18">
       <c r="A116" t="s">
+        <v>164</v>
+      </c>
+      <c r="B116" t="s">
+        <v>165</v>
+      </c>
+      <c r="C116" t="s">
+        <v>20</v>
+      </c>
+      <c r="D116" t="s">
+        <v>87</v>
+      </c>
+      <c r="E116" t="s">
+        <v>39</v>
+      </c>
+      <c r="F116" t="s">
+        <v>23</v>
+      </c>
+      <c r="G116" t="s">
         <v>150</v>
       </c>
-      <c r="B116" t="s">
-        <v>151</v>
-      </c>
-      <c r="C116" t="s">
-        <v>20</v>
-      </c>
-      <c r="D116" t="s">
-        <v>79</v>
-      </c>
-      <c r="E116" t="s">
-        <v>22</v>
+      <c r="H116">
+        <v>19</v>
+      </c>
+      <c r="I116" t="s">
+        <v>41</v>
+      </c>
+      <c r="J116" t="s">
+        <v>185</v>
+      </c>
+      <c r="K116">
+        <v>31</v>
       </c>
       <c r="P116" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q116" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R116" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="117" spans="1:18">
       <c r="A117" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B117" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C117" t="s">
         <v>20</v>
       </c>
       <c r="D117" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E117" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="P117" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q117" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R117" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="118" spans="1:18">
       <c r="A118" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B118" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C118" t="s">
         <v>20</v>
       </c>
       <c r="D118" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="E118" t="s">
-        <v>29</v>
-      </c>
-      <c r="F118" t="s">
-        <v>30</v>
-      </c>
-      <c r="G118" t="s">
-        <v>115</v>
-      </c>
-      <c r="H118">
-        <v>16</v>
-      </c>
-      <c r="I118" t="s">
-        <v>32</v>
-      </c>
-      <c r="J118" t="s">
-        <v>163</v>
-      </c>
-      <c r="K118">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="P118" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q118" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R118" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="119" spans="1:18">
       <c r="A119" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B119" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C119" t="s">
         <v>20</v>
       </c>
       <c r="D119" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E119" t="s">
-        <v>35</v>
+        <v>48</v>
+      </c>
+      <c r="F119" t="s">
+        <v>23</v>
+      </c>
+      <c r="G119" t="s">
+        <v>108</v>
       </c>
       <c r="H119">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="I119" t="s">
+        <v>25</v>
+      </c>
+      <c r="J119" t="s">
+        <v>186</v>
       </c>
       <c r="K119">
-        <v>0</v>
-      </c>
-      <c r="L119" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="P119" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q119" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R119" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="120" spans="1:18">
       <c r="A120" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B120" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C120" t="s">
         <v>20</v>
       </c>
       <c r="D120" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="E120" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F120" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G120" t="s">
-        <v>152</v>
+        <v>108</v>
       </c>
       <c r="H120">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I120" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J120" t="s">
-        <v>164</v>
+        <v>126</v>
       </c>
       <c r="K120">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="P120" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q120" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R120" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="121" spans="1:18">
       <c r="A121" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B121" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C121" t="s">
         <v>20</v>
       </c>
       <c r="D121" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="E121" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F121" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G121" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="H121">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I121" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J121" t="s">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="K121">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="P121" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q121" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R121" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="122" spans="1:18">
-      <c r="A122" t="s">
-        <v>150</v>
-      </c>
-      <c r="B122" t="s">
-        <v>151</v>
-      </c>
-      <c r="C122" t="s">
-        <v>20</v>
-      </c>
-      <c r="D122" t="s">
-        <v>90</v>
-      </c>
-      <c r="E122" t="s">
-        <v>45</v>
-      </c>
-      <c r="F122" t="s">
-        <v>30</v>
-      </c>
-      <c r="G122" t="s">
-        <v>141</v>
-      </c>
-      <c r="H122">
-        <v>25</v>
-      </c>
-      <c r="I122" t="s">
-        <v>47</v>
-      </c>
-      <c r="J122" t="s">
-        <v>166</v>
-      </c>
-      <c r="K122">
-        <v>19</v>
-      </c>
-      <c r="P122" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q122" t="s">
-        <v>24</v>
-      </c>
-      <c r="R122" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="123" spans="1:18">
-      <c r="A123" t="s">
-        <v>150</v>
-      </c>
-      <c r="B123" t="s">
-        <v>151</v>
-      </c>
-      <c r="C123" t="s">
-        <v>20</v>
-      </c>
-      <c r="D123" t="s">
-        <v>93</v>
-      </c>
-      <c r="E123" t="s">
-        <v>22</v>
-      </c>
-      <c r="P123" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q123" t="s">
-        <v>24</v>
-      </c>
-      <c r="R123" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="124" spans="1:18">
-      <c r="A124" t="s">
-        <v>150</v>
-      </c>
-      <c r="B124" t="s">
-        <v>151</v>
-      </c>
-      <c r="C124" t="s">
-        <v>20</v>
-      </c>
-      <c r="D124" t="s">
-        <v>94</v>
-      </c>
-      <c r="E124" t="s">
-        <v>27</v>
-      </c>
-      <c r="P124" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q124" t="s">
-        <v>24</v>
-      </c>
-      <c r="R124" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="125" spans="1:18">
-      <c r="A125" t="s">
-        <v>150</v>
-      </c>
-      <c r="B125" t="s">
-        <v>151</v>
-      </c>
-      <c r="C125" t="s">
-        <v>20</v>
-      </c>
-      <c r="D125" t="s">
-        <v>95</v>
-      </c>
-      <c r="E125" t="s">
-        <v>29</v>
-      </c>
-      <c r="F125" t="s">
-        <v>30</v>
-      </c>
-      <c r="G125" t="s">
-        <v>135</v>
-      </c>
-      <c r="H125">
-        <v>17</v>
-      </c>
-      <c r="I125" t="s">
-        <v>32</v>
-      </c>
-      <c r="J125" t="s">
-        <v>167</v>
-      </c>
-      <c r="K125">
-        <v>28</v>
-      </c>
-      <c r="P125" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q125" t="s">
-        <v>24</v>
-      </c>
-      <c r="R125" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
